--- a/instruction_data/templates/dec_final/Staff_&_Allocation.xlsx
+++ b/instruction_data/templates/dec_final/Staff_&_Allocation.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyle/projects/onesky_financial_agent/instruction_data/templates/dec_final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE5A925B-0C20-CC46-B632-17FE42639C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E7F140-B28D-7B42-9DD2-6EADBD828248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15520" xr2:uid="{24556527-0DC5-1C42-B79D-1B358BC226DD}"/>
+    <workbookView xWindow="0" yWindow="1620" windowWidth="27640" windowHeight="15520" xr2:uid="{24556527-0DC5-1C42-B79D-1B358BC226DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup3_Staff &amp; allocation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lookup3_Staff &amp; allocation'!$A$2:$O$40</definedName>
     <definedName name="CHActCashBalance" localSheetId="0">#REF!</definedName>
@@ -140,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
   <si>
     <t xml:space="preserve">Organisational capacity building </t>
   </si>
@@ -296,6 +293,9 @@
   </si>
   <si>
     <t>Staff Name</t>
+  </si>
+  <si>
+    <t>Nguyen Thi Minh Ngoc</t>
   </si>
 </sst>
 </file>
@@ -480,36 +480,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Transaction List with Splits"/>
-      <sheetName val="BS manual mapping"/>
-      <sheetName val="salary allocation-v2"/>
-      <sheetName val="PIT+SI payment"/>
-      <sheetName val="PIT+SI payment (2)"/>
-      <sheetName val="30 Bank VN Vietnam (VND)"/>
-      <sheetName val="29 Bank VN Vietnam (USD)"/>
-      <sheetName val="34 Bank VN Vietnam (VND)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -832,7 +802,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A2:K41"/>
+  <dimension ref="A2:K42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -2240,6 +2210,41 @@
         <v>0.49</v>
       </c>
     </row>
+    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="4">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:O40" xr:uid="{3AA4DC1E-11DD-4EBF-98C1-6CE519E17664}"/>
   <conditionalFormatting sqref="A1:A38 A41:A1048576">

--- a/instruction_data/templates/dec_final/Staff_&_Allocation.xlsx
+++ b/instruction_data/templates/dec_final/Staff_&_Allocation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyle/projects/onesky_financial_agent/instruction_data/templates/dec_final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E7F140-B28D-7B42-9DD2-6EADBD828248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC75423-F9F0-2B4F-B3B0-42EF53896E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1620" windowWidth="27640" windowHeight="15520" xr2:uid="{24556527-0DC5-1C42-B79D-1B358BC226DD}"/>
+    <workbookView xWindow="0" yWindow="1000" windowWidth="27640" windowHeight="15520" xr2:uid="{24556527-0DC5-1C42-B79D-1B358BC226DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup3_Staff &amp; allocation" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,8 +354,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -421,6 +427,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -428,7 +447,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -451,6 +470,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2211,43 +2235,43 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="4">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4">
-        <v>1</v>
-      </c>
-      <c r="E42" s="4">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4">
-        <v>0</v>
-      </c>
-      <c r="H42" s="4">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4">
-        <v>0</v>
+      <c r="B42" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>0</v>
+      </c>
+      <c r="I42" s="14">
+        <v>0</v>
+      </c>
+      <c r="J42" s="14">
+        <v>0</v>
+      </c>
+      <c r="K42" s="14">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:O40" xr:uid="{3AA4DC1E-11DD-4EBF-98C1-6CE519E17664}"/>
-  <conditionalFormatting sqref="A1:A38 A41:A1048576">
+  <conditionalFormatting sqref="A1:A38 A41 A43:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
